--- a/output/pdf_financials_xlsx/TGLD.xlsx
+++ b/output/pdf_financials_xlsx/TGLD.xlsx
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.668801</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.668801</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.668801</v>
       </c>
     </row>
     <row r="93">
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0.038765</v>
+        <v>-0.016234</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0.458179</v>
+        <v>0.407574</v>
       </c>
       <c r="D118" s="3" t="n">
         <v>0.567387</v>
@@ -3036,7 +3036,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -3296,7 +3300,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>0.668801</v>
       </c>
@@ -3831,7 +3839,11 @@
           <t>Exploration and evaluation assets expenditures</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E38" s="5" t="n">
         <v>-0.054999</v>
       </c>

--- a/output/pdf_financials_xlsx/TGLD.xlsx
+++ b/output/pdf_financials_xlsx/TGLD.xlsx
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.076484</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.032175</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.000324</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.076484</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.032175</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.000324</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.076484</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.032175</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.000324</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">

--- a/output/pdf_financials_xlsx/TGLD.xlsx
+++ b/output/pdf_financials_xlsx/TGLD.xlsx
@@ -3647,7 +3647,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
